--- a/data/trans_orig/IQ27A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, referida por progenitor/a</t>
+          <t>Talla media, en centímetros, declarada por progenitor/a (tasa de respuesta: 90,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>117,55; 128,48</t>
+          <t>117,41; 128,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>114,8; 125,91</t>
+          <t>114,41; 124,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109,79; 122,38</t>
+          <t>110,74; 123,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>129,76; 138,23</t>
+          <t>130,13; 138,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>121,37; 132,14</t>
+          <t>121,11; 131,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>112,6; 125,81</t>
+          <t>113,48; 125,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>112,36; 123,63</t>
+          <t>112,9; 123,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>134,27; 146,7</t>
+          <t>134,27; 146,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>120,63; 128,34</t>
+          <t>120,95; 128,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115,63; 123,88</t>
+          <t>115,52; 123,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113,18; 121,2</t>
+          <t>112,85; 121,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>133,72; 142,04</t>
+          <t>133,72; 141,75</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>113,44; 124,08</t>
+          <t>113,44; 123,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>112,31; 122,53</t>
+          <t>112,46; 122,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>115,89; 126,35</t>
+          <t>115,59; 126,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126,77; 137,45</t>
+          <t>127,28; 137,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>114,69; 125,63</t>
+          <t>115,02; 125,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>114,72; 125,12</t>
+          <t>114,91; 124,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>117,58; 127,69</t>
+          <t>117,92; 127,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>133,62; 143,18</t>
+          <t>134,32; 143,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>115,39; 123,19</t>
+          <t>115,81; 123,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>114,74; 122,17</t>
+          <t>114,93; 122,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118,36; 125,52</t>
+          <t>118,16; 125,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>131,93; 139,41</t>
+          <t>132,05; 139,34</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>123,2; 136,57</t>
+          <t>123,45; 136,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>117,83; 129,71</t>
+          <t>117,53; 128,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>114,77; 127,46</t>
+          <t>114,78; 128,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>126,23; 139,57</t>
+          <t>126,09; 139,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>128,3; 138,74</t>
+          <t>128,56; 139,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>113,31; 124,52</t>
+          <t>113,81; 125,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>120,16; 132,16</t>
+          <t>119,43; 132,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>130,18; 142,8</t>
+          <t>130,34; 142,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>128,18; 136,34</t>
+          <t>128,11; 136,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117,38; 125,18</t>
+          <t>117,25; 125,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>118,8; 128,48</t>
+          <t>119,48; 128,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>130,63; 139,77</t>
+          <t>130,34; 139,71</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>122,09; 129,32</t>
+          <t>122,39; 129,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>115,76; 123,68</t>
+          <t>115,41; 123,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>119,79; 126,98</t>
+          <t>120,11; 126,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127,26; 143,06</t>
+          <t>127,38; 143,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>121,18; 129,24</t>
+          <t>121,72; 129,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>116,18; 124,14</t>
+          <t>115,93; 123,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>121,64; 129,33</t>
+          <t>122,03; 129,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>130,76; 139,88</t>
+          <t>130,78; 139,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>123,22; 128,52</t>
+          <t>123,28; 128,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117,12; 122,75</t>
+          <t>117,14; 122,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122,21; 127,3</t>
+          <t>121,91; 127,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>130,49; 139,35</t>
+          <t>130,4; 139,35</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>122,41; 132,19</t>
+          <t>122,6; 131,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>118,81; 127,95</t>
+          <t>119,06; 127,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123,8; 131,72</t>
+          <t>123,32; 131,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129,16; 137,89</t>
+          <t>128,93; 138,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>127,45; 136,46</t>
+          <t>127,27; 136,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>123,73; 134,26</t>
+          <t>123,87; 134,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>120,69; 129,71</t>
+          <t>120,91; 129,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>132,08; 141,52</t>
+          <t>132,37; 141,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>126,63; 133,28</t>
+          <t>126,63; 133,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122,52; 129,52</t>
+          <t>122,63; 129,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123,62; 129,56</t>
+          <t>123,18; 129,74</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>132,03; 138,79</t>
+          <t>132,09; 138,77</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>126,86; 137,68</t>
+          <t>126,32; 137,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>113,76; 131,05</t>
+          <t>114,08; 132,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>115,85; 131,45</t>
+          <t>116,66; 131,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>130,65; 141,02</t>
+          <t>130,3; 140,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>118,42; 132,89</t>
+          <t>117,46; 132,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>121,02; 133,7</t>
+          <t>120,11; 133,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>122,84; 135,79</t>
+          <t>121,42; 135,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>130,47; 142,33</t>
+          <t>130,69; 142,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124,21; 132,97</t>
+          <t>124,65; 133,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>119,29; 130,77</t>
+          <t>120,25; 130,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>121,65; 131,78</t>
+          <t>121,71; 131,67</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>132,14; 139,97</t>
+          <t>132,21; 140,07</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>123,6; 127,77</t>
+          <t>123,78; 127,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>119,02; 123,41</t>
+          <t>118,78; 123,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120,86; 124,96</t>
+          <t>120,91; 124,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131,05; 137,79</t>
+          <t>131,43; 137,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>125,68; 129,68</t>
+          <t>125,25; 129,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>120,1; 124,53</t>
+          <t>120,34; 124,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>122,38; 126,46</t>
+          <t>122,24; 126,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>134,63; 139,13</t>
+          <t>134,66; 139,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>125,12; 128,24</t>
+          <t>125,22; 128,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120,33; 123,39</t>
+          <t>120,14; 123,24</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122,26; 125,18</t>
+          <t>122,28; 125,18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>133,72; 137,47</t>
+          <t>133,76; 137,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Clase-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>117,41; 128,2</t>
+          <t>117,51; 128,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>114,41; 124,86</t>
+          <t>114,35; 125,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110,74; 123,5</t>
+          <t>110,52; 122,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130,13; 138,47</t>
+          <t>130,06; 138,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>121,11; 131,92</t>
+          <t>121,04; 132,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>113,48; 125,92</t>
+          <t>113,12; 126,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>112,9; 123,42</t>
+          <t>112,66; 123,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>134,27; 146,77</t>
+          <t>134,74; 147,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>120,95; 128,45</t>
+          <t>120,96; 128,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115,52; 123,73</t>
+          <t>115,36; 123,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112,85; 121,81</t>
+          <t>113,39; 121,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>133,72; 141,75</t>
+          <t>133,97; 141,84</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>113,44; 123,87</t>
+          <t>112,9; 123,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>112,46; 122,42</t>
+          <t>111,98; 122,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>115,59; 126,13</t>
+          <t>115,82; 126,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127,28; 137,85</t>
+          <t>126,85; 137,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>115,02; 125,88</t>
+          <t>114,37; 125,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>114,91; 124,6</t>
+          <t>115,29; 125,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>117,92; 127,05</t>
+          <t>118,72; 127,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>134,32; 143,73</t>
+          <t>133,99; 143,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>115,81; 123,31</t>
+          <t>115,28; 122,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>114,93; 122,5</t>
+          <t>114,81; 122,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118,16; 125,36</t>
+          <t>118,37; 125,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>132,05; 139,34</t>
+          <t>132,33; 139,14</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>123,45; 136,54</t>
+          <t>123,57; 136,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>117,53; 128,97</t>
+          <t>118,08; 129,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>114,78; 128,06</t>
+          <t>115,08; 128,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>126,09; 139,37</t>
+          <t>126,32; 140,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>128,56; 139,04</t>
+          <t>128,03; 138,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>113,81; 125,43</t>
+          <t>113,77; 125,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>119,43; 132,36</t>
+          <t>120,06; 132,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>130,34; 142,75</t>
+          <t>130,9; 143,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>128,11; 136,79</t>
+          <t>128,17; 136,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117,25; 125,52</t>
+          <t>117,76; 125,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119,48; 128,33</t>
+          <t>119,31; 128,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>130,34; 139,71</t>
+          <t>130,43; 139,55</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>122,39; 129,8</t>
+          <t>122,23; 129,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>115,41; 123,97</t>
+          <t>115,6; 123,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120,11; 126,85</t>
+          <t>119,83; 126,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127,38; 143,21</t>
+          <t>127,38; 142,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>121,72; 129,93</t>
+          <t>121,52; 129,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>115,93; 123,71</t>
+          <t>116,18; 124,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>122,03; 129,91</t>
+          <t>122,29; 129,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>130,78; 139,92</t>
+          <t>131,03; 140,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>123,28; 128,49</t>
+          <t>122,95; 128,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117,14; 122,74</t>
+          <t>116,77; 122,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121,91; 127,02</t>
+          <t>122,1; 127,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>130,4; 139,35</t>
+          <t>130,88; 140,51</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>122,6; 131,94</t>
+          <t>121,78; 132,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>119,06; 127,59</t>
+          <t>119,09; 127,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123,32; 131,44</t>
+          <t>123,75; 131,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128,93; 138,03</t>
+          <t>128,78; 137,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>127,27; 136,39</t>
+          <t>127,7; 136,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>123,87; 134,64</t>
+          <t>123,56; 134,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>120,91; 129,98</t>
+          <t>121,23; 130,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>132,37; 141,27</t>
+          <t>132,3; 141,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>126,63; 133,21</t>
+          <t>126,73; 133,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122,63; 129,6</t>
+          <t>122,76; 129,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123,18; 129,74</t>
+          <t>123,59; 129,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>132,09; 138,77</t>
+          <t>132,27; 138,63</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>126,32; 137,08</t>
+          <t>126,53; 137,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>114,08; 132,62</t>
+          <t>113,78; 131,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>116,66; 131,8</t>
+          <t>117,18; 131,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>130,3; 140,61</t>
+          <t>130,29; 140,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>117,46; 132,08</t>
+          <t>118,25; 132,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>120,11; 133,44</t>
+          <t>120,84; 134,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>121,42; 135,09</t>
+          <t>122,98; 136,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>130,69; 142,18</t>
+          <t>129,9; 141,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124,65; 133,88</t>
+          <t>124,18; 132,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>120,25; 130,92</t>
+          <t>119,93; 130,79</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>121,71; 131,67</t>
+          <t>121,77; 131,47</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>132,21; 140,07</t>
+          <t>132,38; 140,23</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>123,78; 127,74</t>
+          <t>123,78; 127,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>118,78; 123,23</t>
+          <t>118,69; 123,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120,91; 124,96</t>
+          <t>120,89; 124,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131,43; 137,43</t>
+          <t>131,36; 137,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>125,25; 129,44</t>
+          <t>125,28; 129,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>120,34; 124,72</t>
+          <t>119,96; 124,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>122,24; 126,46</t>
+          <t>122,34; 126,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>134,66; 139,25</t>
+          <t>134,69; 139,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>125,22; 128,18</t>
+          <t>125,14; 127,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120,14; 123,24</t>
+          <t>120,25; 123,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122,28; 125,18</t>
+          <t>122,26; 125,19</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>133,76; 137,49</t>
+          <t>133,61; 137,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Clase-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>126,46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>119,36</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>117,93</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>138,1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>122,8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>119,93</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>116,69</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>134,28</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>126,46</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>119,36</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>117,93</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>139,19</t>
+          <t>134,98</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>137,02</t>
+          <t>136,64</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>117,51; 128,27</t>
+          <t>121,37; 132,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>114,35; 125,42</t>
+          <t>112,6; 125,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110,52; 122,98</t>
+          <t>112,36; 123,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130,06; 138,36</t>
+          <t>132,85; 141,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>121,04; 132,06</t>
+          <t>117,55; 128,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>113,12; 126,21</t>
+          <t>114,8; 125,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>112,66; 123,74</t>
+          <t>109,79; 122,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>134,74; 147,99</t>
+          <t>130,89; 138,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>120,96; 128,37</t>
+          <t>120,63; 128,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115,36; 123,72</t>
+          <t>115,63; 123,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113,39; 121,86</t>
+          <t>113,18; 121,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>133,97; 141,84</t>
+          <t>133,53; 139,43</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>120,26</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>119,94</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122,78</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>140,04</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>118,65</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>117,19</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>121,01</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>132,61</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>120,26</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>119,94</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>122,78</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>138,72</t>
+          <t>133,6</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>135,7</t>
+          <t>136,76</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>112,9; 123,02</t>
+          <t>114,69; 125,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>111,98; 122,73</t>
+          <t>114,72; 125,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>115,82; 126,46</t>
+          <t>117,58; 127,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126,85; 137,6</t>
+          <t>135,1; 144,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>114,37; 125,4</t>
+          <t>113,44; 124,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>115,29; 125,48</t>
+          <t>112,31; 122,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>118,72; 127,94</t>
+          <t>115,89; 126,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>133,99; 143,5</t>
+          <t>128,01; 138,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>115,28; 122,86</t>
+          <t>115,39; 123,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>114,81; 122,31</t>
+          <t>114,74; 122,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118,37; 125,7</t>
+          <t>118,36; 125,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>132,33; 139,14</t>
+          <t>132,9; 140,33</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>133,77</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>119,34</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>126,09</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>138,79</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>130,35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>123,7</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>121,27</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>133,18</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>133,77</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>119,34</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>126,09</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>136,66</t>
+          <t>134,21</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>135,18</t>
+          <t>136,69</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>123,57; 136,64</t>
+          <t>128,3; 138,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>118,08; 129,7</t>
+          <t>113,31; 124,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>115,08; 128,37</t>
+          <t>120,16; 132,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>126,32; 140,01</t>
+          <t>132,01; 144,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>128,03; 138,8</t>
+          <t>123,2; 136,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>113,77; 125,68</t>
+          <t>117,83; 129,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>120,06; 132,84</t>
+          <t>114,77; 127,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>130,9; 143,07</t>
+          <t>127,59; 140,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>128,17; 136,13</t>
+          <t>128,18; 136,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117,76; 125,58</t>
+          <t>117,38; 125,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119,31; 128,65</t>
+          <t>118,8; 128,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>130,43; 139,55</t>
+          <t>132,09; 141,07</t>
         </is>
       </c>
     </row>
@@ -1068,49 +1068,49 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>125,55</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>120,12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>125,74</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>136,29</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>125,93</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>119,91</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>123,47</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>133,3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>125,55</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>120,12</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>132,92</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>125,74</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>135,1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>125,74</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>120,02</t>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>134,19</t>
+          <t>134,68</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>122,23; 129,47</t>
+          <t>121,18; 129,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>115,6; 123,82</t>
+          <t>116,18; 124,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>119,83; 126,78</t>
+          <t>121,64; 129,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127,38; 142,4</t>
+          <t>132,09; 140,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>121,52; 129,22</t>
+          <t>122,09; 129,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>116,18; 124,32</t>
+          <t>115,76; 123,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>122,29; 129,6</t>
+          <t>119,79; 126,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>131,03; 140,15</t>
+          <t>129,08; 136,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>122,95; 128,36</t>
+          <t>123,22; 128,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116,77; 122,69</t>
+          <t>117,12; 122,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122,1; 127,07</t>
+          <t>122,21; 127,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>130,88; 140,51</t>
+          <t>131,77; 137,68</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>132,07</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>129,19</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>125,64</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>137,78</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>127,34</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>123,58</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>127,76</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>133,31</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>132,07</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>129,19</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>125,64</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>136,63</t>
+          <t>133,73</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>135,24</t>
+          <t>136,0</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>121,78; 132,02</t>
+          <t>127,45; 136,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>119,09; 127,96</t>
+          <t>123,73; 134,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123,75; 131,77</t>
+          <t>120,69; 129,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128,78; 137,79</t>
+          <t>133,41; 142,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>127,7; 136,3</t>
+          <t>122,41; 132,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>123,56; 134,56</t>
+          <t>118,81; 127,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>121,23; 130,07</t>
+          <t>123,8; 131,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>132,3; 141,54</t>
+          <t>129,59; 137,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>126,73; 133,23</t>
+          <t>126,63; 133,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122,76; 129,35</t>
+          <t>122,52; 129,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123,59; 129,54</t>
+          <t>123,62; 129,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>132,27; 138,63</t>
+          <t>132,96; 139,12</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>125,46</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>127,39</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>129,1</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>138,97</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>132,23</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>123,21</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>124,46</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>135,72</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>125,46</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>127,39</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>129,1</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>136,57</t>
+          <t>137,8</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>136,17</t>
+          <t>138,41</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>126,53; 137,37</t>
+          <t>118,42; 132,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>113,78; 131,5</t>
+          <t>121,02; 133,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>117,18; 131,53</t>
+          <t>122,84; 135,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>130,29; 140,48</t>
+          <t>132,82; 144,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>118,25; 132,73</t>
+          <t>126,86; 137,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>120,84; 134,54</t>
+          <t>113,76; 131,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>122,98; 136,95</t>
+          <t>115,85; 131,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>129,9; 141,88</t>
+          <t>132,79; 143,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124,18; 132,86</t>
+          <t>124,21; 132,97</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>119,93; 130,79</t>
+          <t>119,29; 130,77</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>121,77; 131,47</t>
+          <t>121,65; 131,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>132,38; 140,23</t>
+          <t>134,73; 142,24</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>127,46</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>122,32</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>124,48</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>137,92</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>125,83</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>121,08</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>122,97</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>133,59</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>127,46</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>122,32</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>124,48</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>136,92</t>
+          <t>134,17</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>135,37</t>
+          <t>136,15</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>123,78; 127,7</t>
+          <t>125,68; 129,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>118,69; 123,12</t>
+          <t>120,1; 124,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120,89; 124,82</t>
+          <t>122,38; 126,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131,36; 137,46</t>
+          <t>135,76; 139,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>125,28; 129,57</t>
+          <t>123,6; 127,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>119,96; 124,43</t>
+          <t>119,02; 123,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>122,34; 126,61</t>
+          <t>120,86; 124,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>134,69; 139,26</t>
+          <t>132,25; 136,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>125,14; 127,93</t>
+          <t>125,12; 128,24</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120,25; 123,36</t>
+          <t>120,33; 123,39</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122,26; 125,19</t>
+          <t>122,26; 125,18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>133,61; 137,41</t>
+          <t>134,67; 137,46</t>
         </is>
       </c>
     </row>
